--- a/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/09,26/08,09,26 ПОКОМ КИ/машины ПОКОМ КИ.xlsx
+++ b/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/09,26/08,09,26 ПОКОМ КИ/машины ПОКОМ КИ.xlsx
@@ -5,17 +5,17 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты ПОКОМ КИ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\ПОКОМ\филиалы НВ\09,26\08,09,26 ПОКОМ КИ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E1C48BB-7CAF-47DB-9C88-1E3CA6924124}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2A0E191-A5E3-4DE1-9F93-FCDEB2D989F7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="181029" refMode="R1C1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -554,7 +554,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -620,6 +620,9 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1053,7 +1056,7 @@
       <c r="Q3" s="6"/>
       <c r="R3" s="3"/>
       <c r="S3" s="7"/>
-      <c r="T3" s="6">
+      <c r="T3" s="45">
         <v>17529</v>
       </c>
       <c r="U3" s="3">
@@ -1076,7 +1079,7 @@
       </c>
       <c r="C4" s="24"/>
       <c r="D4" s="25"/>
-      <c r="E4" s="23">
+      <c r="E4" s="43">
         <v>17389</v>
       </c>
       <c r="F4" s="24">
@@ -1094,7 +1097,7 @@
       <c r="N4" s="4"/>
       <c r="O4" s="2"/>
       <c r="P4" s="5"/>
-      <c r="Q4" s="4">
+      <c r="Q4" s="43">
         <v>16051</v>
       </c>
       <c r="R4" s="2">
@@ -1123,7 +1126,7 @@
       <c r="E5" s="23"/>
       <c r="F5" s="24"/>
       <c r="G5" s="25"/>
-      <c r="H5" s="4">
+      <c r="H5" s="43">
         <v>17615</v>
       </c>
       <c r="I5" s="2">
@@ -1135,7 +1138,7 @@
       <c r="K5" s="4"/>
       <c r="L5" s="2"/>
       <c r="M5" s="5"/>
-      <c r="N5" s="4">
+      <c r="N5" s="43">
         <v>9302</v>
       </c>
       <c r="O5" s="2">
@@ -1174,7 +1177,7 @@
       <c r="H6" s="4"/>
       <c r="I6" s="2"/>
       <c r="J6" s="5"/>
-      <c r="K6" s="4">
+      <c r="K6" s="43">
         <v>17607</v>
       </c>
       <c r="L6" s="24">
@@ -1342,7 +1345,7 @@
       <c r="N11" s="9"/>
       <c r="O11" s="10"/>
       <c r="P11" s="11"/>
-      <c r="Q11" s="26">
+      <c r="Q11" s="44">
         <v>1556</v>
       </c>
       <c r="R11" s="27">
@@ -1441,7 +1444,7 @@
       <c r="K14" s="26"/>
       <c r="L14" s="27"/>
       <c r="M14" s="28"/>
-      <c r="N14" s="26">
+      <c r="N14" s="44">
         <v>964</v>
       </c>
       <c r="O14" s="27">
@@ -1483,7 +1486,7 @@
       <c r="K15" s="23"/>
       <c r="L15" s="24"/>
       <c r="M15" s="25"/>
-      <c r="N15" s="23">
+      <c r="N15" s="43">
         <v>7275</v>
       </c>
       <c r="O15" s="24">
